--- a/documents/Furnace_Startup_Shutdown_Checksheet.xlsx
+++ b/documents/Furnace_Startup_Shutdown_Checksheet.xlsx
@@ -673,7 +673,7 @@
     <t xml:space="preserve">Tray 58 (MW-4512 F2-2610-09)</t>
   </si>
   <si>
-    <t xml:space="preserve">26 empty trays</t>
+    <t xml:space="preserve">25 empty trays</t>
   </si>
   <si>
     <t xml:space="preserve">Line empty</t>
